--- a/development/one_file_rosetta_output/SP109957_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP109957_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E415"/>
+  <dimension ref="A1:F415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -566,7 +578,10 @@
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -676,9 +694,12 @@
         </is>
       </c>
       <c r="D6" s="4">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4">
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -732,9 +753,12 @@
         </is>
       </c>
       <c r="D7" s="4">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -790,7 +814,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -816,9 +843,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -881,7 +911,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -909,7 +942,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -987,7 +1023,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1065,7 +1104,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1093,7 +1135,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1121,7 +1166,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1214,7 +1262,10 @@
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1240,9 +1291,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1296,9 +1350,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>4</v>
+      </c>
+      <c r="E18" s="4">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1352,9 +1409,12 @@
         </is>
       </c>
       <c r="D19" s="4">
+        <v>4</v>
+      </c>
+      <c r="E19" s="4">
         <v>3</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1408,9 +1468,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1471,9 +1534,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1536,7 +1602,10 @@
       <c r="D22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1629,7 +1698,10 @@
       <c r="D23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1655,9 +1727,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>6</v>
+      </c>
+      <c r="E24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1711,9 +1786,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>6</v>
+      </c>
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1767,9 +1845,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>6</v>
+      </c>
+      <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1823,9 +1904,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>3</v>
+      </c>
+      <c r="E27" s="4">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1879,9 +1963,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>13</v>
+      </c>
+      <c r="E28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1935,9 +2022,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>13</v>
+      </c>
+      <c r="E29" s="4">
         <v>2</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1991,9 +2081,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>13</v>
+      </c>
+      <c r="E30" s="4">
         <v>3</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2047,9 +2140,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>13</v>
+      </c>
+      <c r="E31" s="4">
         <v>4</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2103,9 +2199,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>13</v>
+      </c>
+      <c r="E32" s="4">
         <v>5</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2161,7 +2260,10 @@
       <c r="D33" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="4">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2222,9 +2324,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>6</v>
+      </c>
+      <c r="E34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2285,9 +2390,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>6</v>
+      </c>
+      <c r="E35" s="4">
         <v>2</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2348,9 +2456,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>2</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2421,7 +2532,10 @@
       <c r="D37" s="4">
         <v>2</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2492,7 +2606,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2520,7 +2637,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2576,7 +2696,10 @@
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2604,7 +2727,10 @@
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2658,9 +2784,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>4</v>
+      </c>
+      <c r="E42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2723,7 +2852,10 @@
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2794,7 +2926,10 @@
       <c r="D44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2872,7 +3007,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2950,7 +3088,10 @@
       <c r="D46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3034,9 +3175,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3120,9 +3264,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3213,9 +3360,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>2</v>
+      </c>
+      <c r="E49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3308,7 +3458,10 @@
       <c r="D50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3407,9 +3560,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>2</v>
+      </c>
+      <c r="E51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3435,9 +3591,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>3</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3543,9 +3702,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>5</v>
+      </c>
+      <c r="E53" s="4">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3651,9 +3813,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>5</v>
+      </c>
+      <c r="E54" s="4">
         <v>2</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3761,7 +3926,10 @@
       <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3789,7 +3957,10 @@
       <c r="D56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3815,9 +3986,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>2</v>
+      </c>
+      <c r="E57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3933,7 +4107,10 @@
       <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3961,7 +4138,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4017,7 +4197,10 @@
       <c r="D60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="4">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4073,7 +4256,10 @@
       <c r="D61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4101,7 +4287,10 @@
       <c r="D62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4164,7 +4353,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4190,9 +4382,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>2</v>
+      </c>
+      <c r="E64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4268,9 +4463,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>2</v>
+      </c>
+      <c r="E65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4356,7 +4554,10 @@
       <c r="D66" s="4">
         <v>2</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>2</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4440,9 +4641,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>3</v>
+      </c>
+      <c r="E67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4526,9 +4730,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>3</v>
+      </c>
+      <c r="E68" s="4">
         <v>2</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4614,7 +4821,10 @@
       <c r="D69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4707,7 +4917,10 @@
       <c r="D70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4735,7 +4948,10 @@
       <c r="D71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4763,7 +4979,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4864,7 +5083,10 @@
       <c r="D73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4970,9 +5192,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>3</v>
+      </c>
+      <c r="E74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4998,9 +5223,12 @@
         </is>
       </c>
       <c r="D75" s="4">
+        <v>2</v>
+      </c>
+      <c r="E75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5116,7 +5344,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5172,7 +5403,10 @@
       <c r="D77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5200,7 +5434,10 @@
       <c r="D78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5263,7 +5500,10 @@
       <c r="D79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5332,9 +5572,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5405,7 +5648,10 @@
       <c r="D81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5433,7 +5679,10 @@
       <c r="D82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5511,7 +5760,10 @@
       <c r="D83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5539,7 +5791,10 @@
       <c r="D84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5567,7 +5822,10 @@
       <c r="D85" s="4">
         <v>1</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5653,7 +5911,10 @@
       <c r="D86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5681,7 +5942,10 @@
       <c r="D87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5780,9 +6044,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>2</v>
+      </c>
+      <c r="E88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5890,7 +6157,10 @@
       <c r="D89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5918,7 +6188,10 @@
       <c r="D90" s="4">
         <v>1</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5974,7 +6247,10 @@
       <c r="D91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6030,7 +6306,10 @@
       <c r="D92" s="4">
         <v>1</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="4">
+        <v>1</v>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6056,9 +6335,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>2</v>
+      </c>
+      <c r="E93" s="4">
         <v>1</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6086,7 +6368,10 @@
       <c r="D94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6114,7 +6399,10 @@
       <c r="D95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4">
+        <v>1</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6142,7 +6430,10 @@
       <c r="D96" s="4">
         <v>1</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6170,7 +6461,10 @@
       <c r="D97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6278,7 +6572,10 @@
       <c r="D98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="4">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6384,9 +6681,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>3</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6412,9 +6712,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>3</v>
+      </c>
+      <c r="E100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6477,7 +6780,10 @@
       <c r="D101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="4">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6505,7 +6811,10 @@
       <c r="D102" s="4">
         <v>1</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="4">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6531,9 +6840,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>2</v>
+      </c>
+      <c r="E103" s="4">
         <v>1</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6611,7 +6923,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6639,7 +6954,10 @@
       <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6665,9 +6983,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>2</v>
+      </c>
+      <c r="E106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6758,9 +7079,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>5</v>
+      </c>
+      <c r="E107" s="4">
         <v>1</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6851,9 +7175,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>5</v>
+      </c>
+      <c r="E108" s="4">
         <v>2</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6944,9 +7271,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>5</v>
+      </c>
+      <c r="E109" s="4">
         <v>3</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7037,9 +7367,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>5</v>
+      </c>
+      <c r="E110" s="4">
         <v>4</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7132,7 +7465,10 @@
       <c r="D111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="4">
+        <v>1</v>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7158,9 +7494,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>4</v>
+      </c>
+      <c r="E112" s="4">
         <v>1</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7259,9 +7598,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>4</v>
+      </c>
+      <c r="E113" s="4">
         <v>2</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7360,9 +7702,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>4</v>
+      </c>
+      <c r="E114" s="4">
         <v>3</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7463,7 +7808,10 @@
       <c r="D115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7562,9 +7910,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>7</v>
+      </c>
+      <c r="E116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7670,9 +8021,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>7</v>
+      </c>
+      <c r="E117" s="4">
         <v>2</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7778,9 +8132,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>7</v>
+      </c>
+      <c r="E118" s="4">
         <v>3</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7886,9 +8243,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>7</v>
+      </c>
+      <c r="E119" s="4">
         <v>4</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7994,9 +8354,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>7</v>
+      </c>
+      <c r="E120" s="4">
         <v>5</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8102,9 +8465,12 @@
         </is>
       </c>
       <c r="D121" s="4">
+        <v>10</v>
+      </c>
+      <c r="E121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8210,9 +8576,12 @@
         </is>
       </c>
       <c r="D122" s="4">
+        <v>10</v>
+      </c>
+      <c r="E122" s="4">
         <v>2</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8318,9 +8687,12 @@
         </is>
       </c>
       <c r="D123" s="4">
+        <v>10</v>
+      </c>
+      <c r="E123" s="4">
         <v>3</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8426,9 +8798,12 @@
         </is>
       </c>
       <c r="D124" s="4">
+        <v>8</v>
+      </c>
+      <c r="E124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8534,9 +8909,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>8</v>
+      </c>
+      <c r="E125" s="4">
         <v>2</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8642,9 +9020,12 @@
         </is>
       </c>
       <c r="D126" s="4">
+        <v>8</v>
+      </c>
+      <c r="E126" s="4">
         <v>3</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8750,9 +9131,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>8</v>
+      </c>
+      <c r="E127" s="4">
         <v>4</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8858,9 +9242,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>8</v>
+      </c>
+      <c r="E128" s="4">
         <v>5</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8966,9 +9353,12 @@
         </is>
       </c>
       <c r="D129" s="4">
+        <v>7</v>
+      </c>
+      <c r="E129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9082,9 +9472,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>7</v>
+      </c>
+      <c r="E130" s="4">
         <v>2</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9198,9 +9591,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>7</v>
+      </c>
+      <c r="E131" s="4">
         <v>3</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9314,9 +9710,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>7</v>
+      </c>
+      <c r="E132" s="4">
         <v>4</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9430,9 +9829,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>6</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9546,9 +9948,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>6</v>
+      </c>
+      <c r="E134" s="4">
         <v>2</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9662,9 +10067,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>4</v>
+      </c>
+      <c r="E135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9778,9 +10186,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>2</v>
+      </c>
+      <c r="E136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9901,9 +10312,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>5</v>
+      </c>
+      <c r="E137" s="4">
         <v>1</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10024,9 +10438,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>5</v>
+      </c>
+      <c r="E138" s="4">
         <v>2</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10147,9 +10564,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>5</v>
+      </c>
+      <c r="E139" s="4">
         <v>3</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10270,9 +10690,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>5</v>
+      </c>
+      <c r="E140" s="4">
         <v>4</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10395,7 +10818,10 @@
       <c r="D141" s="4">
         <v>1</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="4">
+        <v>1</v>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10423,7 +10849,10 @@
       <c r="D142" s="4">
         <v>1</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="4">
+        <v>1</v>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10477,9 +10906,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>2</v>
+      </c>
+      <c r="E143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10542,7 +10974,10 @@
       <c r="D144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10605,7 +11040,10 @@
       <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10676,7 +11114,10 @@
       <c r="D146" s="4">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10745,9 +11186,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>2</v>
+      </c>
+      <c r="E147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10818,7 +11262,10 @@
       <c r="D148" s="4">
         <v>2</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="4">
+        <v>2</v>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10889,7 +11336,10 @@
       <c r="D149" s="4">
         <v>1</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="4">
+        <v>1</v>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10915,9 +11365,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>2</v>
+      </c>
+      <c r="E150" s="4">
         <v>1</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10995,7 +11448,10 @@
       <c r="D151" s="4">
         <v>2</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="4">
+        <v>2</v>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11073,7 +11529,10 @@
       <c r="D152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="4">
+        <v>1</v>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11159,7 +11618,10 @@
       <c r="D153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="4">
+        <v>1</v>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11187,7 +11649,10 @@
       <c r="D154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="4">
+        <v>1</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11213,9 +11678,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>2</v>
+      </c>
+      <c r="E155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11241,9 +11709,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>5</v>
+      </c>
+      <c r="E156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11342,9 +11813,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>5</v>
+      </c>
+      <c r="E157" s="4">
         <v>2</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11443,9 +11917,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>3</v>
+      </c>
+      <c r="E158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11544,9 +12021,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>3</v>
+      </c>
+      <c r="E159" s="4">
         <v>2</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11647,7 +12127,10 @@
       <c r="D160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="4">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11753,9 +12236,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>2</v>
+      </c>
+      <c r="E161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11861,9 +12347,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>4</v>
+      </c>
+      <c r="E162" s="4">
         <v>1</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11969,9 +12458,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>5</v>
+      </c>
+      <c r="E163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12085,9 +12577,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>5</v>
+      </c>
+      <c r="E164" s="4">
         <v>2</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12203,7 +12698,10 @@
       <c r="D165" s="4">
         <v>1</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="4">
+        <v>1</v>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12317,9 +12815,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>2</v>
+      </c>
+      <c r="E166" s="4">
         <v>1</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12435,7 +12936,10 @@
       <c r="D167" s="4">
         <v>2</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="4">
+        <v>2</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12551,7 +13055,10 @@
       <c r="D168" s="4">
         <v>1</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="4">
+        <v>1</v>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12674,7 +13181,10 @@
       <c r="D169" s="4">
         <v>1</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="4">
+        <v>1</v>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12795,9 +13305,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>3</v>
+      </c>
+      <c r="E170" s="4">
         <v>1</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12920,7 +13433,10 @@
       <c r="D171" s="4">
         <v>1</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="4">
+        <v>1</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12946,9 +13462,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>4</v>
+      </c>
+      <c r="E172" s="4">
         <v>1</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13009,9 +13528,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>4</v>
+      </c>
+      <c r="E173" s="4">
         <v>2</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13072,9 +13594,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>4</v>
+      </c>
+      <c r="E174" s="4">
         <v>3</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13137,7 +13662,10 @@
       <c r="D175" s="4">
         <v>1</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="4">
+        <v>1</v>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13165,7 +13693,10 @@
       <c r="D176" s="4">
         <v>1</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="4">
+        <v>1</v>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13193,7 +13724,10 @@
       <c r="D177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="4">
+        <v>1</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13284,9 +13818,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>2</v>
+      </c>
+      <c r="E178" s="4">
         <v>1</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13385,9 +13922,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>3</v>
+      </c>
+      <c r="E179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13486,9 +14026,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>2</v>
+      </c>
+      <c r="E180" s="4">
         <v>1</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13594,9 +14137,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>4</v>
+      </c>
+      <c r="E181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13702,9 +14248,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>3</v>
+      </c>
+      <c r="E182" s="4">
         <v>1</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13810,9 +14359,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>3</v>
+      </c>
+      <c r="E183" s="4">
         <v>2</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13920,7 +14472,10 @@
       <c r="D184" s="4">
         <v>3</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="4">
+        <v>3</v>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14026,9 +14581,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>3</v>
+      </c>
+      <c r="E185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14142,9 +14700,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>3</v>
+      </c>
+      <c r="E186" s="4">
         <v>2</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14258,9 +14819,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>3</v>
+      </c>
+      <c r="E187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14374,9 +14938,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>4</v>
+      </c>
+      <c r="E188" s="4">
         <v>1</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14402,9 +14969,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>6</v>
+      </c>
+      <c r="E189" s="4">
         <v>1</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14525,9 +15095,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>6</v>
+      </c>
+      <c r="E190" s="4">
         <v>2</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14648,9 +15221,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>2</v>
+      </c>
+      <c r="E191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14678,7 +15254,10 @@
       <c r="D192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="4">
+        <v>1</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14799,9 +15378,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>5</v>
+      </c>
+      <c r="E193" s="4">
         <v>1</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14855,9 +15437,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>5</v>
+      </c>
+      <c r="E194" s="4">
         <v>2</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14911,9 +15496,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>5</v>
+      </c>
+      <c r="E195" s="4">
         <v>3</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14967,9 +15555,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>5</v>
+      </c>
+      <c r="E196" s="4">
         <v>4</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15025,7 +15616,10 @@
       <c r="D197" s="4">
         <v>5</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="4">
+        <v>5</v>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15081,7 +15675,10 @@
       <c r="D198" s="4">
         <v>1</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="4">
+        <v>1</v>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15135,9 +15732,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>5</v>
+      </c>
+      <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15191,9 +15791,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>5</v>
+      </c>
+      <c r="E200" s="4">
         <v>2</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15247,9 +15850,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>5</v>
+      </c>
+      <c r="E201" s="4">
         <v>3</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15303,9 +15909,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>5</v>
+      </c>
+      <c r="E202" s="4">
         <v>4</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15361,7 +15970,10 @@
       <c r="D203" s="4">
         <v>5</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="4">
+        <v>5</v>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15415,9 +16027,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>5</v>
+      </c>
+      <c r="E204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15471,9 +16086,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>5</v>
+      </c>
+      <c r="E205" s="4">
         <v>2</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15527,9 +16145,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>5</v>
+      </c>
+      <c r="E206" s="4">
         <v>3</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15583,9 +16204,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>5</v>
+      </c>
+      <c r="E207" s="4">
         <v>4</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15641,7 +16265,10 @@
       <c r="D208" s="4">
         <v>5</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>5</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15697,7 +16324,10 @@
       <c r="D209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15753,7 +16383,10 @@
       <c r="D210" s="4">
         <v>1</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="4">
+        <v>1</v>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15807,9 +16440,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>2</v>
+      </c>
+      <c r="E211" s="4">
         <v>1</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15865,7 +16501,10 @@
       <c r="D212" s="4">
         <v>2</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="4">
+        <v>2</v>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15921,7 +16560,10 @@
       <c r="D213" s="4">
         <v>1</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="4">
+        <v>1</v>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15977,7 +16619,10 @@
       <c r="D214" s="4">
         <v>1</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="4">
+        <v>1</v>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16031,9 +16676,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>6</v>
+      </c>
+      <c r="E215" s="4">
         <v>1</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16087,9 +16735,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>6</v>
+      </c>
+      <c r="E216" s="4">
         <v>2</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16143,9 +16794,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>6</v>
+      </c>
+      <c r="E217" s="4">
         <v>3</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16199,9 +16853,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>6</v>
+      </c>
+      <c r="E218" s="4">
         <v>4</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16255,9 +16912,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>6</v>
+      </c>
+      <c r="E219" s="4">
         <v>5</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16313,7 +16973,10 @@
       <c r="D220" s="4">
         <v>6</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="4">
+        <v>6</v>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16367,9 +17030,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>3</v>
+      </c>
+      <c r="E221" s="4">
         <v>1</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16439,9 +17105,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>3</v>
+      </c>
+      <c r="E222" s="4">
         <v>2</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16511,9 +17180,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>4</v>
+      </c>
+      <c r="E223" s="4">
         <v>1</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16574,9 +17246,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>4</v>
+      </c>
+      <c r="E224" s="4">
         <v>2</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16637,9 +17312,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>4</v>
+      </c>
+      <c r="E225" s="4">
         <v>3</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16702,7 +17380,10 @@
       <c r="D226" s="4">
         <v>4</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="4">
+        <v>4</v>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16763,9 +17444,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>2</v>
+      </c>
+      <c r="E227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16836,7 +17520,10 @@
       <c r="D228" s="4">
         <v>2</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="4">
+        <v>2</v>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16935,9 +17622,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>9</v>
+      </c>
+      <c r="E229" s="4">
         <v>1</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16998,9 +17688,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>9</v>
+      </c>
+      <c r="E230" s="4">
         <v>2</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17061,9 +17754,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>9</v>
+      </c>
+      <c r="E231" s="4">
         <v>3</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17124,9 +17820,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>9</v>
+      </c>
+      <c r="E232" s="4">
         <v>4</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17187,9 +17886,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>9</v>
+      </c>
+      <c r="E233" s="4">
         <v>5</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17250,9 +17952,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>9</v>
+      </c>
+      <c r="E234" s="4">
         <v>6</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17313,9 +18018,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>9</v>
+      </c>
+      <c r="E235" s="4">
         <v>7</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17376,9 +18084,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>9</v>
+      </c>
+      <c r="E236" s="4">
         <v>8</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17441,7 +18152,10 @@
       <c r="D237" s="4">
         <v>9</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="4">
+        <v>9</v>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17502,9 +18216,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>6</v>
+      </c>
+      <c r="E238" s="4">
         <v>1</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17573,9 +18290,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>6</v>
+      </c>
+      <c r="E239" s="4">
         <v>2</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17644,9 +18364,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>6</v>
+      </c>
+      <c r="E240" s="4">
         <v>3</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17715,9 +18438,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>6</v>
+      </c>
+      <c r="E241" s="4">
         <v>4</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17786,9 +18512,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>6</v>
+      </c>
+      <c r="E242" s="4">
         <v>5</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17859,7 +18588,10 @@
       <c r="D243" s="4">
         <v>6</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="4">
+        <v>6</v>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17928,9 +18660,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>3</v>
+      </c>
+      <c r="E244" s="4">
         <v>1</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18006,9 +18741,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>3</v>
+      </c>
+      <c r="E245" s="4">
         <v>2</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18086,7 +18824,10 @@
       <c r="D246" s="4">
         <v>3</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="4">
+        <v>3</v>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18162,9 +18903,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>2</v>
+      </c>
+      <c r="E247" s="4">
         <v>1</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18257,7 +19001,10 @@
       <c r="D248" s="4">
         <v>2</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="4">
+        <v>2</v>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18350,7 +19097,10 @@
       <c r="D249" s="4">
         <v>1</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E249" s="4">
+        <v>1</v>
+      </c>
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18422,7 +19172,10 @@
       <c r="D250" s="4">
         <v>1</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E250" s="4">
+        <v>1</v>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18492,9 +19245,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>10</v>
+      </c>
+      <c r="E251" s="4">
         <v>1</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18555,9 +19311,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>10</v>
+      </c>
+      <c r="E252" s="4">
         <v>2</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18618,9 +19377,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>10</v>
+      </c>
+      <c r="E253" s="4">
         <v>3</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18681,9 +19443,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>10</v>
+      </c>
+      <c r="E254" s="4">
         <v>4</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18744,9 +19509,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>10</v>
+      </c>
+      <c r="E255" s="4">
         <v>5</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18807,9 +19575,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>10</v>
+      </c>
+      <c r="E256" s="4">
         <v>6</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18870,9 +19641,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>10</v>
+      </c>
+      <c r="E257" s="4">
         <v>7</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18933,9 +19707,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>10</v>
+      </c>
+      <c r="E258" s="4">
         <v>8</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18996,9 +19773,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>10</v>
+      </c>
+      <c r="E259" s="4">
         <v>9</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19061,7 +19841,10 @@
       <c r="D260" s="4">
         <v>10</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="E260" s="4">
+        <v>10</v>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19124,7 +19907,10 @@
       <c r="D261" s="4">
         <v>1</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E261" s="4">
+        <v>1</v>
+      </c>
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19200,9 +19986,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>7</v>
+      </c>
+      <c r="E262" s="4">
         <v>1</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19286,9 +20075,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>7</v>
+      </c>
+      <c r="E263" s="4">
         <v>2</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19372,9 +20164,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>7</v>
+      </c>
+      <c r="E264" s="4">
         <v>3</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19465,9 +20260,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>7</v>
+      </c>
+      <c r="E265" s="4">
         <v>4</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19551,9 +20349,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>7</v>
+      </c>
+      <c r="E266" s="4">
         <v>5</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19697,9 +20498,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>7</v>
+      </c>
+      <c r="E267" s="4">
         <v>6</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19807,7 +20611,10 @@
       <c r="D268" s="4">
         <v>7</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="4">
+        <v>7</v>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19908,7 +20715,10 @@
       <c r="D269" s="4">
         <v>1</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="4">
+        <v>1</v>
+      </c>
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19978,9 +20788,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>2</v>
+      </c>
+      <c r="E270" s="4">
         <v>1</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20043,7 +20856,10 @@
       <c r="D271" s="4">
         <v>2</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="4">
+        <v>2</v>
+      </c>
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20104,9 +20920,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>2</v>
+      </c>
+      <c r="E272" s="4">
         <v>1</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20177,7 +20996,10 @@
       <c r="D273" s="4">
         <v>2</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="E273" s="4">
+        <v>2</v>
+      </c>
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20246,9 +21068,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>7</v>
+      </c>
+      <c r="E274" s="4">
         <v>1</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20324,9 +21149,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>7</v>
+      </c>
+      <c r="E275" s="4">
         <v>2</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20402,9 +21230,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>7</v>
+      </c>
+      <c r="E276" s="4">
         <v>3</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20480,9 +21311,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>7</v>
+      </c>
+      <c r="E277" s="4">
         <v>4</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20558,9 +21392,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>7</v>
+      </c>
+      <c r="E278" s="4">
         <v>5</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20636,9 +21473,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>7</v>
+      </c>
+      <c r="E279" s="4">
         <v>6</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20716,7 +21556,10 @@
       <c r="D280" s="4">
         <v>1</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="E280" s="4">
+        <v>1</v>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20779,7 +21622,10 @@
       <c r="D281" s="4">
         <v>1</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="E281" s="4">
+        <v>1</v>
+      </c>
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20893,9 +21739,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>5</v>
+      </c>
+      <c r="E282" s="4">
         <v>1</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20965,9 +21814,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>5</v>
+      </c>
+      <c r="E283" s="4">
         <v>2</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21028,9 +21880,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>5</v>
+      </c>
+      <c r="E284" s="4">
         <v>3</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21100,9 +21955,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>5</v>
+      </c>
+      <c r="E285" s="4">
         <v>4</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21174,7 +22032,10 @@
       <c r="D286" s="4">
         <v>5</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="E286" s="4">
+        <v>5</v>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21244,9 +22105,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>5</v>
+      </c>
+      <c r="E287" s="4">
         <v>1</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21316,9 +22180,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>5</v>
+      </c>
+      <c r="E288" s="4">
         <v>2</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21379,9 +22246,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>5</v>
+      </c>
+      <c r="E289" s="4">
         <v>3</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21451,9 +22321,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>5</v>
+      </c>
+      <c r="E290" s="4">
         <v>4</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21516,7 +22389,10 @@
       <c r="D291" s="4">
         <v>5</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="4">
+        <v>5</v>
+      </c>
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21586,9 +22462,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>2</v>
+      </c>
+      <c r="E292" s="4">
         <v>1</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21644,7 +22523,10 @@
       <c r="D293" s="4">
         <v>2</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="4">
+        <v>2</v>
+      </c>
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21698,9 +22580,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>4</v>
+      </c>
+      <c r="E294" s="4">
         <v>1</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21754,9 +22639,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>4</v>
+      </c>
+      <c r="E295" s="4">
         <v>2</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21810,9 +22698,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>4</v>
+      </c>
+      <c r="E296" s="4">
         <v>3</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21866,9 +22757,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>4</v>
+      </c>
+      <c r="E297" s="4">
         <v>1</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21938,9 +22832,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>4</v>
+      </c>
+      <c r="E298" s="4">
         <v>2</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22010,9 +22907,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>4</v>
+      </c>
+      <c r="E299" s="4">
         <v>3</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22084,7 +22984,10 @@
       <c r="D300" s="4">
         <v>4</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="4">
+        <v>4</v>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22154,9 +23057,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>2</v>
+      </c>
+      <c r="E301" s="4">
         <v>1</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22219,7 +23125,10 @@
       <c r="D302" s="4">
         <v>2</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="E302" s="4">
+        <v>2</v>
+      </c>
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22282,7 +23191,10 @@
       <c r="D303" s="4">
         <v>1</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="E303" s="4">
+        <v>1</v>
+      </c>
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22351,9 +23263,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>6</v>
+      </c>
+      <c r="E304" s="4">
         <v>1</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22414,9 +23329,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>6</v>
+      </c>
+      <c r="E305" s="4">
         <v>2</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22477,9 +23395,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>6</v>
+      </c>
+      <c r="E306" s="4">
         <v>3</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22540,9 +23461,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>6</v>
+      </c>
+      <c r="E307" s="4">
         <v>4</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22603,9 +23527,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>6</v>
+      </c>
+      <c r="E308" s="4">
         <v>5</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22668,7 +23595,10 @@
       <c r="D309" s="4">
         <v>6</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="4">
+        <v>6</v>
+      </c>
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22731,7 +23661,10 @@
       <c r="D310" s="4">
         <v>1</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="E310" s="4">
+        <v>1</v>
+      </c>
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22802,7 +23735,10 @@
       <c r="D311" s="4">
         <v>1</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="E311" s="4">
+        <v>1</v>
+      </c>
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22886,9 +23822,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>5</v>
+      </c>
+      <c r="E312" s="4">
         <v>1</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22979,9 +23918,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>5</v>
+      </c>
+      <c r="E313" s="4">
         <v>2</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23072,9 +24014,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>5</v>
+      </c>
+      <c r="E314" s="4">
         <v>3</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23165,9 +24110,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>5</v>
+      </c>
+      <c r="E315" s="4">
         <v>4</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23260,7 +24208,10 @@
       <c r="D316" s="4">
         <v>5</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="4">
+        <v>5</v>
+      </c>
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23351,9 +24302,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>5</v>
+      </c>
+      <c r="E317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23414,9 +24368,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>5</v>
+      </c>
+      <c r="E318" s="4">
         <v>2</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23477,9 +24434,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>5</v>
+      </c>
+      <c r="E319" s="4">
         <v>3</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23540,9 +24500,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>5</v>
+      </c>
+      <c r="E320" s="4">
         <v>4</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23605,7 +24568,10 @@
       <c r="D321" s="4">
         <v>5</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="4">
+        <v>5</v>
+      </c>
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23668,7 +24634,10 @@
       <c r="D322" s="4">
         <v>1</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="4">
+        <v>1</v>
+      </c>
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23739,7 +24708,10 @@
       <c r="D323" s="4">
         <v>1</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="4">
+        <v>1</v>
+      </c>
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23838,9 +24810,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>11</v>
+      </c>
+      <c r="E324" s="4">
         <v>1</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23901,9 +24876,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>11</v>
+      </c>
+      <c r="E325" s="4">
         <v>2</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23964,9 +24942,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>11</v>
+      </c>
+      <c r="E326" s="4">
         <v>3</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24027,9 +25008,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>11</v>
+      </c>
+      <c r="E327" s="4">
         <v>4</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24090,9 +25074,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>11</v>
+      </c>
+      <c r="E328" s="4">
         <v>5</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24153,9 +25140,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>11</v>
+      </c>
+      <c r="E329" s="4">
         <v>6</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24216,9 +25206,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>11</v>
+      </c>
+      <c r="E330" s="4">
         <v>7</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24279,9 +25272,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>11</v>
+      </c>
+      <c r="E331" s="4">
         <v>8</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24342,9 +25338,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>11</v>
+      </c>
+      <c r="E332" s="4">
         <v>9</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24405,9 +25404,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>11</v>
+      </c>
+      <c r="E333" s="4">
         <v>10</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24470,7 +25472,10 @@
       <c r="D334" s="4">
         <v>1</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="E334" s="4">
+        <v>1</v>
+      </c>
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24554,9 +25559,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>2</v>
+      </c>
+      <c r="E335" s="4">
         <v>1</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24649,7 +25657,10 @@
       <c r="D336" s="4">
         <v>2</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="E336" s="4">
+        <v>2</v>
+      </c>
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24763,9 +25774,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>43</v>
+      </c>
+      <c r="E337" s="4">
         <v>1</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24826,9 +25840,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>43</v>
+      </c>
+      <c r="E338" s="4">
         <v>2</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24889,9 +25906,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>43</v>
+      </c>
+      <c r="E339" s="4">
         <v>3</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24952,9 +25972,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>43</v>
+      </c>
+      <c r="E340" s="4">
         <v>4</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25015,9 +26038,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>43</v>
+      </c>
+      <c r="E341" s="4">
         <v>5</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25078,9 +26104,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>43</v>
+      </c>
+      <c r="E342" s="4">
         <v>6</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25141,9 +26170,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>43</v>
+      </c>
+      <c r="E343" s="4">
         <v>7</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25204,9 +26236,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>43</v>
+      </c>
+      <c r="E344" s="4">
         <v>8</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25267,9 +26302,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>43</v>
+      </c>
+      <c r="E345" s="4">
         <v>9</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25330,9 +26368,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>43</v>
+      </c>
+      <c r="E346" s="4">
         <v>10</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25393,9 +26434,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>43</v>
+      </c>
+      <c r="E347" s="4">
         <v>11</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25456,9 +26500,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>43</v>
+      </c>
+      <c r="E348" s="4">
         <v>12</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25519,9 +26566,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>43</v>
+      </c>
+      <c r="E349" s="4">
         <v>13</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25582,9 +26632,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>43</v>
+      </c>
+      <c r="E350" s="4">
         <v>14</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25645,9 +26698,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>43</v>
+      </c>
+      <c r="E351" s="4">
         <v>15</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25708,9 +26764,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>43</v>
+      </c>
+      <c r="E352" s="4">
         <v>16</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25771,9 +26830,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>43</v>
+      </c>
+      <c r="E353" s="4">
         <v>17</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25834,9 +26896,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>43</v>
+      </c>
+      <c r="E354" s="4">
         <v>18</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25897,9 +26962,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>43</v>
+      </c>
+      <c r="E355" s="4">
         <v>19</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25960,9 +27028,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>43</v>
+      </c>
+      <c r="E356" s="4">
         <v>20</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26025,7 +27096,10 @@
       <c r="D357" s="4">
         <v>1</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="E357" s="4">
+        <v>1</v>
+      </c>
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26124,9 +27198,12 @@
         </is>
       </c>
       <c r="D358" s="4">
+        <v>5</v>
+      </c>
+      <c r="E358" s="4">
         <v>1</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26196,9 +27273,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>5</v>
+      </c>
+      <c r="E359" s="4">
         <v>2</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26268,9 +27348,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>5</v>
+      </c>
+      <c r="E360" s="4">
         <v>3</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26340,9 +27423,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>5</v>
+      </c>
+      <c r="E361" s="4">
         <v>4</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26414,7 +27500,10 @@
       <c r="D362" s="4">
         <v>5</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="E362" s="4">
+        <v>5</v>
+      </c>
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26484,9 +27573,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>2</v>
+      </c>
+      <c r="E363" s="4">
         <v>1</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26558,7 +27650,10 @@
       <c r="D364" s="4">
         <v>2</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="E364" s="4">
+        <v>2</v>
+      </c>
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26628,9 +27723,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>8</v>
+      </c>
+      <c r="E365" s="4">
         <v>1</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26700,9 +27798,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>8</v>
+      </c>
+      <c r="E366" s="4">
         <v>2</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26772,9 +27873,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>8</v>
+      </c>
+      <c r="E367" s="4">
         <v>3</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26844,9 +27948,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>8</v>
+      </c>
+      <c r="E368" s="4">
         <v>4</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26907,9 +28014,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>8</v>
+      </c>
+      <c r="E369" s="4">
         <v>5</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26979,9 +28089,12 @@
         </is>
       </c>
       <c r="D370" s="4">
+        <v>8</v>
+      </c>
+      <c r="E370" s="4">
         <v>6</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27051,9 +28164,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>8</v>
+      </c>
+      <c r="E371" s="4">
         <v>7</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27125,7 +28241,10 @@
       <c r="D372" s="4">
         <v>8</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="E372" s="4">
+        <v>8</v>
+      </c>
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27195,9 +28314,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>5</v>
+      </c>
+      <c r="E373" s="4">
         <v>1</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27267,9 +28389,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>5</v>
+      </c>
+      <c r="E374" s="4">
         <v>2</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27339,9 +28464,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>5</v>
+      </c>
+      <c r="E375" s="4">
         <v>3</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27411,9 +28539,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>5</v>
+      </c>
+      <c r="E376" s="4">
         <v>4</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27485,7 +28616,10 @@
       <c r="D377" s="4">
         <v>5</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="E377" s="4">
+        <v>5</v>
+      </c>
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27555,9 +28689,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>3</v>
+      </c>
+      <c r="E378" s="4">
         <v>1</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27627,9 +28764,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>3</v>
+      </c>
+      <c r="E379" s="4">
         <v>2</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27701,7 +28841,10 @@
       <c r="D380" s="4">
         <v>3</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="E380" s="4">
+        <v>3</v>
+      </c>
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27771,9 +28914,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>6</v>
+      </c>
+      <c r="E381" s="4">
         <v>1</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27843,9 +28989,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>6</v>
+      </c>
+      <c r="E382" s="4">
         <v>2</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27915,9 +29064,12 @@
         </is>
       </c>
       <c r="D383" s="4">
+        <v>6</v>
+      </c>
+      <c r="E383" s="4">
         <v>3</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27987,9 +29139,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>6</v>
+      </c>
+      <c r="E384" s="4">
         <v>4</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28059,9 +29214,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>6</v>
+      </c>
+      <c r="E385" s="4">
         <v>5</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28133,7 +29291,10 @@
       <c r="D386" s="4">
         <v>6</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="E386" s="4">
+        <v>6</v>
+      </c>
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28203,9 +29364,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>2</v>
+      </c>
+      <c r="E387" s="4">
         <v>1</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28277,7 +29441,10 @@
       <c r="D388" s="4">
         <v>2</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="E388" s="4">
+        <v>2</v>
+      </c>
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28347,9 +29514,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>2</v>
+      </c>
+      <c r="E389" s="4">
         <v>1</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28421,7 +29591,10 @@
       <c r="D390" s="4">
         <v>2</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="E390" s="4">
+        <v>2</v>
+      </c>
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28493,7 +29666,10 @@
       <c r="D391" s="4">
         <v>1</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="E391" s="4">
+        <v>1</v>
+      </c>
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28563,9 +29739,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>2</v>
+      </c>
+      <c r="E392" s="4">
         <v>1</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28637,7 +29816,10 @@
       <c r="D393" s="4">
         <v>2</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="E393" s="4">
+        <v>2</v>
+      </c>
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28707,9 +29889,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>9</v>
+      </c>
+      <c r="E394" s="4">
         <v>1</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28779,9 +29964,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>9</v>
+      </c>
+      <c r="E395" s="4">
         <v>2</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28851,9 +30039,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>9</v>
+      </c>
+      <c r="E396" s="4">
         <v>3</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28923,9 +30114,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>9</v>
+      </c>
+      <c r="E397" s="4">
         <v>4</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28995,9 +30189,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>9</v>
+      </c>
+      <c r="E398" s="4">
         <v>5</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29067,9 +30264,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>9</v>
+      </c>
+      <c r="E399" s="4">
         <v>6</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29139,9 +30339,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>9</v>
+      </c>
+      <c r="E400" s="4">
         <v>7</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29211,9 +30414,12 @@
         </is>
       </c>
       <c r="D401" s="4">
+        <v>9</v>
+      </c>
+      <c r="E401" s="4">
         <v>8</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29285,7 +30491,10 @@
       <c r="D402" s="4">
         <v>9</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="E402" s="4">
+        <v>9</v>
+      </c>
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29355,9 +30564,12 @@
         </is>
       </c>
       <c r="D403" s="4">
+        <v>6</v>
+      </c>
+      <c r="E403" s="4">
         <v>1</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29427,9 +30639,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>6</v>
+      </c>
+      <c r="E404" s="4">
         <v>2</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29499,9 +30714,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>6</v>
+      </c>
+      <c r="E405" s="4">
         <v>3</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29571,9 +30789,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>6</v>
+      </c>
+      <c r="E406" s="4">
         <v>4</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29643,9 +30864,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>6</v>
+      </c>
+      <c r="E407" s="4">
         <v>5</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29717,7 +30941,10 @@
       <c r="D408" s="4">
         <v>6</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="E408" s="4">
+        <v>6</v>
+      </c>
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29787,9 +31014,12 @@
         </is>
       </c>
       <c r="D409" s="4">
+        <v>2</v>
+      </c>
+      <c r="E409" s="4">
         <v>1</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29861,7 +31091,10 @@
       <c r="D410" s="4">
         <v>2</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="E410" s="4">
+        <v>2</v>
+      </c>
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29933,7 +31166,10 @@
       <c r="D411" s="4">
         <v>1</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="E411" s="4">
+        <v>1</v>
+      </c>
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30003,9 +31239,12 @@
         </is>
       </c>
       <c r="D412" s="4">
+        <v>2</v>
+      </c>
+      <c r="E412" s="4">
         <v>1</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30077,7 +31316,10 @@
       <c r="D413" s="4">
         <v>2</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="E413" s="4">
+        <v>2</v>
+      </c>
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30147,9 +31389,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>2</v>
+      </c>
+      <c r="E414" s="4">
         <v>1</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30221,7 +31466,10 @@
       <c r="D415" s="4">
         <v>2</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="E415" s="4">
+        <v>2</v>
+      </c>
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30275,220 +31523,291 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="213">
+  <mergeCells count="284">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
     <mergeCell ref="A28:A32"/>
     <mergeCell ref="B28:B32"/>
     <mergeCell ref="C28:C32"/>
+    <mergeCell ref="D28:D32"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="B53:B54"/>
     <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="B65:B66"/>
     <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
     <mergeCell ref="A107:A110"/>
     <mergeCell ref="B107:B110"/>
     <mergeCell ref="C107:C110"/>
+    <mergeCell ref="D107:D110"/>
     <mergeCell ref="A112:A114"/>
     <mergeCell ref="B112:B114"/>
     <mergeCell ref="C112:C114"/>
+    <mergeCell ref="D112:D114"/>
     <mergeCell ref="A116:A120"/>
     <mergeCell ref="B116:B120"/>
     <mergeCell ref="C116:C120"/>
+    <mergeCell ref="D116:D120"/>
     <mergeCell ref="A121:A123"/>
     <mergeCell ref="B121:B123"/>
     <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D121:D123"/>
     <mergeCell ref="A124:A128"/>
     <mergeCell ref="B124:B128"/>
     <mergeCell ref="C124:C128"/>
+    <mergeCell ref="D124:D128"/>
     <mergeCell ref="A129:A132"/>
     <mergeCell ref="B129:B132"/>
     <mergeCell ref="C129:C132"/>
+    <mergeCell ref="D129:D132"/>
     <mergeCell ref="A133:A134"/>
     <mergeCell ref="B133:B134"/>
     <mergeCell ref="C133:C134"/>
+    <mergeCell ref="D133:D134"/>
     <mergeCell ref="A137:A140"/>
     <mergeCell ref="B137:B140"/>
     <mergeCell ref="C137:C140"/>
+    <mergeCell ref="D137:D140"/>
     <mergeCell ref="A147:A148"/>
     <mergeCell ref="B147:B148"/>
     <mergeCell ref="C147:C148"/>
+    <mergeCell ref="D147:D148"/>
     <mergeCell ref="A150:A151"/>
     <mergeCell ref="B150:B151"/>
     <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
     <mergeCell ref="A156:A157"/>
     <mergeCell ref="B156:B157"/>
     <mergeCell ref="C156:C157"/>
+    <mergeCell ref="D156:D157"/>
     <mergeCell ref="A158:A159"/>
     <mergeCell ref="B158:B159"/>
     <mergeCell ref="C158:C159"/>
+    <mergeCell ref="D158:D159"/>
     <mergeCell ref="A163:A164"/>
     <mergeCell ref="B163:B164"/>
     <mergeCell ref="C163:C164"/>
+    <mergeCell ref="D163:D164"/>
     <mergeCell ref="A166:A167"/>
     <mergeCell ref="B166:B167"/>
     <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
     <mergeCell ref="A172:A174"/>
     <mergeCell ref="B172:B174"/>
     <mergeCell ref="C172:C174"/>
+    <mergeCell ref="D172:D174"/>
     <mergeCell ref="A182:A184"/>
     <mergeCell ref="B182:B184"/>
     <mergeCell ref="C182:C184"/>
+    <mergeCell ref="D182:D184"/>
     <mergeCell ref="A185:A186"/>
     <mergeCell ref="B185:B186"/>
     <mergeCell ref="C185:C186"/>
+    <mergeCell ref="D185:D186"/>
     <mergeCell ref="A189:A190"/>
     <mergeCell ref="B189:B190"/>
     <mergeCell ref="C189:C190"/>
+    <mergeCell ref="D189:D190"/>
     <mergeCell ref="A193:A197"/>
     <mergeCell ref="B193:B197"/>
     <mergeCell ref="C193:C197"/>
+    <mergeCell ref="D193:D197"/>
     <mergeCell ref="A199:A203"/>
     <mergeCell ref="B199:B203"/>
     <mergeCell ref="C199:C203"/>
+    <mergeCell ref="D199:D203"/>
     <mergeCell ref="A204:A208"/>
     <mergeCell ref="B204:B208"/>
     <mergeCell ref="C204:C208"/>
+    <mergeCell ref="D204:D208"/>
     <mergeCell ref="A211:A212"/>
     <mergeCell ref="B211:B212"/>
     <mergeCell ref="C211:C212"/>
+    <mergeCell ref="D211:D212"/>
     <mergeCell ref="A215:A220"/>
     <mergeCell ref="B215:B220"/>
     <mergeCell ref="C215:C220"/>
+    <mergeCell ref="D215:D220"/>
     <mergeCell ref="A221:A222"/>
     <mergeCell ref="B221:B222"/>
     <mergeCell ref="C221:C222"/>
+    <mergeCell ref="D221:D222"/>
     <mergeCell ref="A223:A226"/>
     <mergeCell ref="B223:B226"/>
     <mergeCell ref="C223:C226"/>
+    <mergeCell ref="D223:D226"/>
     <mergeCell ref="A227:A228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="C227:C228"/>
+    <mergeCell ref="D227:D228"/>
     <mergeCell ref="A229:A237"/>
     <mergeCell ref="B229:B237"/>
     <mergeCell ref="C229:C237"/>
+    <mergeCell ref="D229:D237"/>
     <mergeCell ref="A238:A243"/>
     <mergeCell ref="B238:B243"/>
     <mergeCell ref="C238:C243"/>
+    <mergeCell ref="D238:D243"/>
     <mergeCell ref="A244:A246"/>
     <mergeCell ref="B244:B246"/>
     <mergeCell ref="C244:C246"/>
+    <mergeCell ref="D244:D246"/>
     <mergeCell ref="A247:A248"/>
     <mergeCell ref="B247:B248"/>
     <mergeCell ref="C247:C248"/>
+    <mergeCell ref="D247:D248"/>
     <mergeCell ref="A251:A260"/>
     <mergeCell ref="B251:B260"/>
     <mergeCell ref="C251:C260"/>
+    <mergeCell ref="D251:D260"/>
     <mergeCell ref="A262:A268"/>
     <mergeCell ref="B262:B268"/>
     <mergeCell ref="C262:C268"/>
+    <mergeCell ref="D262:D268"/>
     <mergeCell ref="A270:A271"/>
     <mergeCell ref="B270:B271"/>
     <mergeCell ref="C270:C271"/>
+    <mergeCell ref="D270:D271"/>
     <mergeCell ref="A272:A273"/>
     <mergeCell ref="B272:B273"/>
     <mergeCell ref="C272:C273"/>
+    <mergeCell ref="D272:D273"/>
     <mergeCell ref="A274:A279"/>
     <mergeCell ref="B274:B279"/>
     <mergeCell ref="C274:C279"/>
+    <mergeCell ref="D274:D279"/>
     <mergeCell ref="A282:A286"/>
     <mergeCell ref="B282:B286"/>
     <mergeCell ref="C282:C286"/>
+    <mergeCell ref="D282:D286"/>
     <mergeCell ref="A287:A291"/>
     <mergeCell ref="B287:B291"/>
     <mergeCell ref="C287:C291"/>
+    <mergeCell ref="D287:D291"/>
     <mergeCell ref="A292:A293"/>
     <mergeCell ref="B292:B293"/>
     <mergeCell ref="C292:C293"/>
+    <mergeCell ref="D292:D293"/>
     <mergeCell ref="A294:A296"/>
     <mergeCell ref="B294:B296"/>
     <mergeCell ref="C294:C296"/>
+    <mergeCell ref="D294:D296"/>
     <mergeCell ref="A297:A300"/>
     <mergeCell ref="B297:B300"/>
     <mergeCell ref="C297:C300"/>
+    <mergeCell ref="D297:D300"/>
     <mergeCell ref="A301:A302"/>
     <mergeCell ref="B301:B302"/>
     <mergeCell ref="C301:C302"/>
+    <mergeCell ref="D301:D302"/>
     <mergeCell ref="A304:A309"/>
     <mergeCell ref="B304:B309"/>
     <mergeCell ref="C304:C309"/>
+    <mergeCell ref="D304:D309"/>
     <mergeCell ref="A312:A316"/>
     <mergeCell ref="B312:B316"/>
     <mergeCell ref="C312:C316"/>
+    <mergeCell ref="D312:D316"/>
     <mergeCell ref="A317:A321"/>
     <mergeCell ref="B317:B321"/>
     <mergeCell ref="C317:C321"/>
+    <mergeCell ref="D317:D321"/>
     <mergeCell ref="A324:A333"/>
     <mergeCell ref="B324:B333"/>
     <mergeCell ref="C324:C333"/>
+    <mergeCell ref="D324:D333"/>
     <mergeCell ref="A335:A336"/>
     <mergeCell ref="B335:B336"/>
     <mergeCell ref="C335:C336"/>
+    <mergeCell ref="D335:D336"/>
     <mergeCell ref="A337:A356"/>
     <mergeCell ref="B337:B356"/>
     <mergeCell ref="C337:C356"/>
+    <mergeCell ref="D337:D356"/>
     <mergeCell ref="A358:A362"/>
     <mergeCell ref="B358:B362"/>
     <mergeCell ref="C358:C362"/>
+    <mergeCell ref="D358:D362"/>
     <mergeCell ref="A363:A364"/>
     <mergeCell ref="B363:B364"/>
     <mergeCell ref="C363:C364"/>
+    <mergeCell ref="D363:D364"/>
     <mergeCell ref="A365:A372"/>
     <mergeCell ref="B365:B372"/>
     <mergeCell ref="C365:C372"/>
+    <mergeCell ref="D365:D372"/>
     <mergeCell ref="A373:A377"/>
     <mergeCell ref="B373:B377"/>
     <mergeCell ref="C373:C377"/>
+    <mergeCell ref="D373:D377"/>
     <mergeCell ref="A378:A380"/>
     <mergeCell ref="B378:B380"/>
     <mergeCell ref="C378:C380"/>
+    <mergeCell ref="D378:D380"/>
     <mergeCell ref="A381:A386"/>
     <mergeCell ref="B381:B386"/>
     <mergeCell ref="C381:C386"/>
+    <mergeCell ref="D381:D386"/>
     <mergeCell ref="A387:A388"/>
     <mergeCell ref="B387:B388"/>
     <mergeCell ref="C387:C388"/>
+    <mergeCell ref="D387:D388"/>
     <mergeCell ref="A389:A390"/>
     <mergeCell ref="B389:B390"/>
     <mergeCell ref="C389:C390"/>
+    <mergeCell ref="D389:D390"/>
     <mergeCell ref="A392:A393"/>
     <mergeCell ref="B392:B393"/>
     <mergeCell ref="C392:C393"/>
+    <mergeCell ref="D392:D393"/>
     <mergeCell ref="A394:A402"/>
     <mergeCell ref="B394:B402"/>
     <mergeCell ref="C394:C402"/>
+    <mergeCell ref="D394:D402"/>
     <mergeCell ref="A403:A408"/>
     <mergeCell ref="B403:B408"/>
     <mergeCell ref="C403:C408"/>
+    <mergeCell ref="D403:D408"/>
     <mergeCell ref="A409:A410"/>
     <mergeCell ref="B409:B410"/>
     <mergeCell ref="C409:C410"/>
+    <mergeCell ref="D409:D410"/>
     <mergeCell ref="A412:A413"/>
     <mergeCell ref="B412:B413"/>
     <mergeCell ref="C412:C413"/>
+    <mergeCell ref="D412:D413"/>
     <mergeCell ref="A414:A415"/>
     <mergeCell ref="B414:B415"/>
     <mergeCell ref="C414:C415"/>
+    <mergeCell ref="D414:D415"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
